--- a/data_extactor/batch_10_fa/trimmed/batch_0086_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0086_fa_trim.xlsx
@@ -513,12 +513,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>تولید و فراوری</t>
+          <t>تولید و فرآوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>کنترل دقیق | چابکی دستی | دید نزدیک | حساسیت به مسئله | هماهنگی چندعضوی | پایداری دست و بازو | چابکی انگشتان</t>
+          <t>دقت کنترل | مهارت دستی | بینایی نزدیک | حساسیت به مسئله | هماهنگی چند عضو | ثبات دست و بازو | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تنظیم‌کاران و اپراتورهای ماشین‌های برشکاری، منگنه‌زنی و پرس فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های دریل‌کاری و بورینگ فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین تراش و تراشکاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | سنگ‌زن‌ها، سوهان‌کاران و تیزکنندگان ابزار</t>
+          <t>تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | شنیدن فعال</t>
+          <t>درک مطلب | نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید و فراوری | مکانیک | مهندسی و فناوری | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | ریاضیات</t>
+          <t>تولید و فرآوری | مکانیک | مهندسی و فناوری | مدیریت و اداره | خدمات مشتری و شخصی | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>پایداری دست و بازو | کنترل دقیق | دید نزدیک | چابکی انگشتان | هماهنگی چندعضوی | چابکی دستی | تجسم فضایی</t>
+          <t>ثبات دست و بازو | دقت کنترل | بینایی نزدیک | مهارت انگشتان | هماهنگی چند عضو | مهارت دستی | تجسم</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتورهای ابزارهای CNC | تنظیم‌کاران و اپراتورهای ماشین‌های دریل‌کاری و بورینگ فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تراشکاران و ماشین‌کاران | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | قالب‌سازان و ابزارسازان</t>
+          <t>اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | قالب‌سازان و ابزارسازان صنعتی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | شنیدن فعال</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و فراوری | زبان انگلیسی | ریاضیات | رایانه و الکترونیک</t>
+          <t>مکانیک | تولید و فرآوری | زبان انگلیسی | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>چابکی دستی | دید نزدیک | کنترل دقیق | پایداری دست و بازو | حساسیت به مسئله | چابکی انگشتان | تجسم فضایی</t>
+          <t>مهارت دستی | بینایی نزدیک | دقت کنترل | ثبات دست و بازو | حساسیت به مسئله | مهارت انگشتان | تجسم</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>اپراتورهای ابزارهای CNC | تنظیم‌کاران و اپراتورهای ماشین‌های دریل‌کاری و بورینگ فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین تراش و تراشکاری فلز و پلاستیک | تراشکاران و ماشین‌کاران | قالب‌سازان و ابزارسازان</t>
+          <t>اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای سوراخ‌کاری و حفاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | قالب‌سازان و ابزارسازان صنعتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ریاضیات | مکانیک | تولید و فراوری | طراحی</t>
+          <t>ریاضیات | مکانیک | تولید و فرآوری | طراحی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>پایداری دست و بازو | چابکی دستی | چابکی انگشتان | کنترل دقیق | دید نزدیک | حساسیت به مسئله | تجسم فضایی</t>
+          <t>ثبات دست و بازو | مهارت دستی | مهارت انگشتان | دقت کنترل | بینایی نزدیک | حساسیت به مسئله | تجسم</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کارشناسان و تکنسین‌های کالیبراسیون | اپراتورهای ابزارهای CNC | برنامه‌نویسان ماشین‌های کنترل عددی رایانه‌ای CNC | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین تراش و تراشکاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | قالب‌سازان و ابزارسازان</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | برنامه‌نویسان ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | قالب‌سازان و ابزارسازان صنعتی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>تولید و فراوری | مکانیک | ایمنی و امنیت عمومی | مدیریت و امور اداری | آموزش و تدریس</t>
+          <t>تولید و فرآوری | مکانیک | ایمنی و امنیت عمومی | مدیریت و اداره | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>کنترل دقیق | حساسیت به مسئله | چابکی دستی | دید نزدیک | زمان واکنش | پایداری دست و بازو | کنترل نرخ</t>
+          <t>دقت کنترل | حساسیت به مسئله | مهارت دستی | بینایی نزدیک | زمان عکس‌العمل | ثبات دست و بازو | کنترل نرخ</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و اتوکلاوها | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | ریخته‌گران و متصدیان بارریزی مذاب فلزات | تعمیرکاران و نسوزکاران مواد دیرگداز به‌جز بناها | تنظیم‌کاران و اپراتورهای ماشین‌های نورد فلز و پلاستیک</t>
+          <t>اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | ریخته‌گران و متصدیان بارریزی مذاب فلزات | تعمیرکاران و نسوزکاران مواد دیرگداز صنعتی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>پایداری دست و بازو | کنترل دقیق | چابکی دستی | دید نزدیک | زمان واکنش | هماهنگی چندعضوی | استحکام بالاتنه</t>
+          <t>ثبات دست و بازو | دقت کنترل | مهارت دستی | بینایی نزدیک | زمان عکس‌العمل | هماهنگی چند عضو | قدرت تنه</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>قالب‌گیران و ماهیچه‌سازان ریخته‌گری | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و متصدیان تخلیه خطوط ماشین‌کاری | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های آبکاری و پوشش‌دهی فلز و پلاستیک | تعمیرکاران و نسوزکاران مواد دیرگداز به‌جز بناها</t>
+          <t>قالب‌گیران و ماهیچه‌سازان ریخته‌گری | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای دستگاه‌های آبکاری فلز و پلاستیک | تعمیرکاران و نسوزکاران مواد دیرگداز صنعتی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -855,12 +855,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مکانیک | ریاضیات | تولید و فراوری | طراحی | مهندسی و فناوری</t>
+          <t>مکانیک | ریاضیات | تولید و فرآوری | طراحی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | تجسم فضایی | پایداری دست و بازو | چابکی دستی | چابکی انگشتان | کنترل دقیق | مرتب‌سازی اطلاعات</t>
+          <t>بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | دقت کنترل | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>اپراتورهای ابزارهای CNC | برنامه‌نویسان ماشین‌های کنترل عددی رایانه‌ای CNC | خط‌کش‌ها و نشانه‌گذاران فلز و پلاستیک | تراشکاران و ماشین‌کاران | نقشه‌کش‌های مکانیک | الگو سازان فلز و پلاستیک | قالب‌سازان و ابزارسازان</t>
+          <t>اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | برنامه‌نویسان ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | نقشه‌کشان مکانیک | الگوسازان فلز و پلاستیک | قالب‌سازان و ابزارسازان صنعتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,22 +902,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3D Systems Geomagic Design X | Autodesk AutoCAD | Delcam PowerMILL | نرم‌افزار CAD/CAM طراحی و ساخت Mastercam | Microsoft Excel | Microsoft Outlook</t>
+          <t>3D Systems Geomagic Design X | Autodesk AutoCAD | Delcam PowerMILL | نرم‌افزار طراحی و تولید به کمک کامپیوتر Mastercam | Microsoft Excel | Microsoft Outlook</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و فراوری | مکانیک | ریاضیات | طراحی | مهندسی و فناوری</t>
+          <t>تولید و فرآوری | مکانیک | ریاضیات | طراحی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | پایداری دست و بازو | حساسیت به مسئله | تجسم فضایی | چابکی دستی | کنترل دقیق | چابکی انگشتان</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | حساسیت به مسئله | تجسم | مهارت دستی | دقت کنترل | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>خط‌کش‌ها و نشانه‌گذاران فلز و پلاستیک | تراشکاران و ماشین‌کاران | نقشه‌کش‌های مکانیک | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | قالب‌ریزان و فرم‌دهندگان به‌جز فلز و پلاستیک | قالب‌سازان و ابزارسازان</t>
+          <t>خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | نقشه‌کشان مکانیک | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مدل‌سازان فلز و پلاستیک | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | قالب‌سازان و ابزارسازان صنعتی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و فراوری | مدیریت و امور اداری | فیزیک | طراحی | مهندسی و فناوری</t>
+          <t>مکانیک | تولید و فرآوری | مدیریت و اداره | فیزیک | طراحی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>استحکام بالاتنه | چابکی دستی | قدرت ایستا | پایداری دست و بازو | چابکی انگشتان | هماهنگی چندعضوی | دید نزدیک</t>
+          <t>قدرت تنه | مهارت دستی | قدرت ایستا | ثبات دست و بازو | مهارت انگشتان | هماهنگی چند عضو | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کارگران سنگ‌زنی و پرداخت دستی | تغذیه‌کنندگان و متصدیان تخلیه خطوط ماشین‌کاری | قالب‌ریزان و فرم‌دهندگان به‌جز فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | الگو سازان فلز و پلاستیک | تعمیرکاران و نسوزکاران مواد دیرگداز به‌جز بناها | قالب‌سازان و ابزارسازان</t>
+          <t>پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | الگوسازان فلز و پلاستیک | تعمیرکاران و نسوزکاران مواد دیرگداز صنعتی | قالب‌سازان و ابزارسازان صنعتی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | درک مطلب | تفکر انتقادی | سخن گفتن</t>
+          <t>گوش دادن فعال | نظارت | درک مطلب | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>تولید و فراوری | مکانیک | ریاضیات</t>
+          <t>تولید و فرآوری | مکانیک | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>پایداری دست و بازو | چابکی دستی | هماهنگی چندعضوی | کنترل دقیق | مرتب‌سازی اطلاعات | دید نزدیک | حساسیت به مسئله</t>
+          <t>ثبات دست و بازو | مهارت دستی | هماهنگی چند عضو | دقت کنترل | ترتیب‌دهی اطلاعات | بینایی نزدیک | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تنظیم‌کاران و اپراتورهای ماشین‌های برشکاری، منگنه‌زنی و پرس فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های آهنگری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | قالب‌ریزان و فرم‌دهندگان به‌جز فلز و پلاستیک | قالب‌سازان و ابزارسازان</t>
+          <t>تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | قالب‌سازان و ابزارسازان صنعتی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
